--- a/migracion/archivo.xlsx
+++ b/migracion/archivo.xlsx
@@ -3,20 +3,15 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Hoja1" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="Hoja1" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr/>
-  <extLst>
-    <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="EXwRoECwgzcxit/LSv9bFnw1eiAHcNcHvIy6V+7rWqs="/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>CODIGO 1X10</t>
   </si>
@@ -59,104 +54,11 @@
   <si>
     <t>CORREO ELECTRONICO</t>
   </si>
-  <si>
-    <t>Juana</t>
-  </si>
-  <si>
-    <t>Rafaela</t>
-  </si>
-  <si>
-    <t>Guzman</t>
-  </si>
-  <si>
-    <t>Blanco</t>
-  </si>
-  <si>
-    <t>Caracas</t>
-  </si>
-  <si>
-    <t>Libertador</t>
-  </si>
-  <si>
-    <t>Altagracia</t>
-  </si>
-  <si>
-    <t>juana33@yopamil.com</t>
-  </si>
-  <si>
-    <t>Martin</t>
-  </si>
-  <si>
-    <t>Alejandro</t>
-  </si>
-  <si>
-    <t>Roa</t>
-  </si>
-  <si>
-    <t>Piere</t>
-  </si>
-  <si>
-    <t>martin86@yopmail.com</t>
-  </si>
-  <si>
-    <t>Yudith</t>
-  </si>
-  <si>
-    <t>Martina</t>
-  </si>
-  <si>
-    <t>Lopez</t>
-  </si>
-  <si>
-    <t>Herrera</t>
-  </si>
-  <si>
-    <t>yudith33@yopamil.com</t>
-  </si>
-  <si>
-    <t>Isarael</t>
-  </si>
-  <si>
-    <t>Hierro</t>
-  </si>
-  <si>
-    <t>Federal</t>
-  </si>
-  <si>
-    <t>israel22@yopamil.com</t>
-  </si>
-  <si>
-    <t>Petra</t>
-  </si>
-  <si>
-    <t>Dianicio</t>
-  </si>
-  <si>
-    <t>Yural</t>
-  </si>
-  <si>
-    <t>pedro123@yopamil.com</t>
-  </si>
-  <si>
-    <t>Miguel</t>
-  </si>
-  <si>
-    <t>Luna</t>
-  </si>
-  <si>
-    <t>Horacio</t>
-  </si>
-  <si>
-    <t>miguel643@yopamil.com</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="dd-mm-yyyy"/>
-  </numFmts>
   <fonts count="3">
     <font>
       <sz val="11.0"/>
@@ -171,9 +73,9 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11.0"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -210,16 +112,13 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -232,6 +131,10 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -506,269 +409,14 @@
       <c r="Z1" s="2"/>
     </row>
     <row r="2">
-      <c r="A2" s="3">
-        <v>864848.0</v>
-      </c>
-      <c r="B2" s="4">
-        <v>46072.0</v>
-      </c>
-      <c r="C2" s="3">
-        <v>2.1589632E7</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H2" s="4">
-        <v>25147.0</v>
-      </c>
-      <c r="I2" s="3">
-        <v>2.127689928E9</v>
-      </c>
-      <c r="J2" s="3">
-        <v>4.167893253E9</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>21</v>
-      </c>
+      <c r="A2" s="3"/>
     </row>
-    <row r="3">
-      <c r="A3" s="3">
-        <v>991848.0</v>
-      </c>
-      <c r="B3" s="4">
-        <v>46072.0</v>
-      </c>
-      <c r="C3" s="3">
-        <v>2.4213689E7</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H3" s="4">
-        <v>37321.0</v>
-      </c>
-      <c r="I3" s="3">
-        <v>2.127621484E9</v>
-      </c>
-      <c r="J3" s="3">
-        <v>4.167893253E9</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3">
-        <v>777416.0</v>
-      </c>
-      <c r="B4" s="4">
-        <v>46072.0</v>
-      </c>
-      <c r="C4" s="3">
-        <v>2.7893664E7</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="H4" s="4">
-        <v>24966.0</v>
-      </c>
-      <c r="I4" s="3">
-        <v>2.127689928E9</v>
-      </c>
-      <c r="J4" s="3">
-        <v>4.167893253E9</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N4" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3">
-        <v>648847.0</v>
-      </c>
-      <c r="B5" s="4">
-        <v>46072.0</v>
-      </c>
-      <c r="C5" s="3">
-        <v>2.2645232E7</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="H5" s="4">
-        <v>36473.0</v>
-      </c>
-      <c r="I5" s="3">
-        <v>2.127689928E9</v>
-      </c>
-      <c r="J5" s="3">
-        <v>4.167893253E9</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N5" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3">
-        <v>154884.0</v>
-      </c>
-      <c r="B6" s="4">
-        <v>46072.0</v>
-      </c>
-      <c r="C6" s="3">
-        <v>3.0752634E7</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="H6" s="4">
-        <v>24973.0</v>
-      </c>
-      <c r="I6" s="3">
-        <v>2.127689928E9</v>
-      </c>
-      <c r="J6" s="3">
-        <v>4.167893253E9</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N6" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3">
-        <v>218484.0</v>
-      </c>
-      <c r="B7" s="4">
-        <v>46077.0</v>
-      </c>
-      <c r="C7" s="3">
-        <v>1.9623422E7</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="H7" s="4">
-        <v>34753.0</v>
-      </c>
-      <c r="I7" s="3">
-        <v>2.127689928E9</v>
-      </c>
-      <c r="J7" s="3">
-        <v>4.167893253E9</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="M7" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N7" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
+    <row r="15" ht="15.75" customHeight="1"/>
+    <row r="16" ht="15.75" customHeight="1"/>
+    <row r="17" ht="15.75" customHeight="1"/>
+    <row r="18" ht="15.75" customHeight="1"/>
+    <row r="19" ht="15.75" customHeight="1"/>
+    <row r="20" ht="15.75" customHeight="1"/>
     <row r="21" ht="15.75" customHeight="1"/>
     <row r="22" ht="15.75" customHeight="1"/>
     <row r="23" ht="15.75" customHeight="1"/>
@@ -1743,12 +1391,6 @@
     <row r="992" ht="15.75" customHeight="1"/>
     <row r="993" ht="15.75" customHeight="1"/>
     <row r="994" ht="15.75" customHeight="1"/>
-    <row r="995" ht="15.75" customHeight="1"/>
-    <row r="996" ht="15.75" customHeight="1"/>
-    <row r="997" ht="15.75" customHeight="1"/>
-    <row r="998" ht="15.75" customHeight="1"/>
-    <row r="999" ht="15.75" customHeight="1"/>
-    <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
